--- a/datac.xlsx
+++ b/datac.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416"/>
   </bookViews>
   <sheets>
-    <sheet name="SIEGE" sheetId="1" r:id="rId1"/>
+    <sheet name="feuille1" sheetId="1" r:id="rId1"/>
     <sheet name="DONNEES" sheetId="4" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>

--- a/datac.xlsx
+++ b/datac.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416"/>
   </bookViews>
   <sheets>
-    <sheet name="feuille1" sheetId="1" r:id="rId1"/>
+    <sheet name="feuil 1" sheetId="1" r:id="rId1"/>
     <sheet name="DONNEES" sheetId="4" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
